--- a/excel/WalgamaMart_Dashboard.xlsx
+++ b/excel/WalgamaMart_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chehan\Desktop\Retail-Sales-Profitability-Intelligence-Excel\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DDD1BE9-7962-4298-822A-9AFE68BA320A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04A4744F-94B3-4C61-BBC7-E72D561C0E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="637" activeTab="1" xr2:uid="{BF65397B-50A1-4D9F-A9A6-D4E19A7FEE21}"/>
   </bookViews>
@@ -28,7 +28,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="4" r:id="rId8"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -3647,7 +3647,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -3663,130 +3663,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="55">
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center"/>
-    </dxf>
+  <dxfs count="16">
     <dxf>
       <alignment horizontal="center"/>
     </dxf>
@@ -5455,8 +5337,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5621,7 +5502,7 @@
         <c:idx val="3"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:solidFill>
@@ -6344,49 +6225,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -9299,6 +9138,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
+            <a:pPr/>
             <a:t>15033192.35</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
@@ -9501,6 +9341,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
+            <a:pPr/>
             <a:t>2700692.352</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
@@ -9703,6 +9544,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
+            <a:pPr/>
             <a:t>0.179648626</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
@@ -9905,6 +9747,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
+            <a:pPr/>
             <a:t>500</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
@@ -10107,6 +9950,7 @@
               </a:solidFill>
               <a:latin typeface="Aptos Narrow"/>
             </a:rPr>
+            <a:pPr/>
             <a:t>1560</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
@@ -10309,6 +10153,7 @@
               </a:solidFill>
               <a:latin typeface="Arial Unicode MS"/>
             </a:rPr>
+            <a:pPr/>
             <a:t>30066.3847</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2400" b="1">
@@ -10397,8 +10242,8 @@
       <xdr:rowOff>153247</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5268649" cy="823906"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="55" name="StoreID">
@@ -10421,7 +10266,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -10470,8 +10315,8 @@
       <xdr:rowOff>23078</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3782839" cy="760686"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="56" name="SalesChannel">
@@ -10494,7 +10339,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -10593,6 +10438,108 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>507703</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>65308</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>415173</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>143644</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12FC6BBE-B905-8C78-4640-615D2FF560BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="1890" t="26766" r="1732" b="30277"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1116122" y="248424"/>
+          <a:ext cx="4166400" cy="627685"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>579551</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>10733</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>611172</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B3161E6-623D-211D-B554-BE22BB407612}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect l="3827" t="16364" r="2495" b="18245"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9755748" y="193184"/>
+          <a:ext cx="3090354" cy="719070"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -20576,7 +20523,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{73E004DD-6D5E-4219-A05B-E6D438E36545}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{73E004DD-6D5E-4219-A05B-E6D438E36545}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="8">
   <location ref="B1:C12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -21067,7 +21014,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5ECDCA41-4CED-495C-9ED9-B0339676E4AE}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5ECDCA41-4CED-495C-9ED9-B0339676E4AE}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="4">
   <location ref="B3:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -21506,7 +21453,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90D4CC86-1D97-4CE5-8F10-7A6AF16AD7E4}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="7">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{90D4CC86-1D97-4CE5-8F10-7A6AF16AD7E4}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="7">
   <location ref="E3:F24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -21994,7 +21941,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5424DC34-5CA7-4EF8-BE3A-D805C31B066A}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5424DC34-5CA7-4EF8-BE3A-D805C31B066A}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" multipleFieldFilters="0" chartFormat="9">
   <location ref="A1:C7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
     <pivotField showAll="0"/>
@@ -22422,7 +22369,7 @@
     <dataField name="Sum of GrossProfit" fld="15" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="3">
-    <format dxfId="39">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -22431,7 +22378,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="40">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1">
@@ -22440,7 +22387,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="0">
       <pivotArea field="4" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
   </formats>
@@ -22572,33 +22519,33 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1DA8362D-E429-45B4-89D0-45CC87CD71D9}" name="sales" displayName="sales" ref="A1:Q501" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:Q501" xr:uid="{1DA8362D-E429-45B4-89D0-45CC87CD71D9}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{56D8A25A-DBED-4BCD-A623-898A46481927}" uniqueName="1" name="OrderID" queryTableFieldId="1" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{6E2A5EBC-A63D-4121-B5FB-803BDD06D63A}" uniqueName="2" name="LineID" queryTableFieldId="2" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{EF3573A2-B3AE-4D91-911B-574EE8BC7624}" uniqueName="3" name="Date" queryTableFieldId="3" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{11AC5243-14B7-4A35-B9B2-1665859BA500}" uniqueName="4" name="ProductID" queryTableFieldId="4" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{0E27DE63-90A7-49BC-A53A-8C102D6575E5}" uniqueName="5" name="StoreID" queryTableFieldId="5" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{F70E5803-CDE6-4E04-B0AC-E66A70250924}" uniqueName="6" name="CustomerID" queryTableFieldId="6" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{532F1CDF-B2EF-44D9-B43C-76A3BAE9BC36}" uniqueName="7" name="SalesChannel" queryTableFieldId="7" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{56D8A25A-DBED-4BCD-A623-898A46481927}" uniqueName="1" name="OrderID" queryTableFieldId="1" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{6E2A5EBC-A63D-4121-B5FB-803BDD06D63A}" uniqueName="2" name="LineID" queryTableFieldId="2" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{EF3573A2-B3AE-4D91-911B-574EE8BC7624}" uniqueName="3" name="Date" queryTableFieldId="3" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{11AC5243-14B7-4A35-B9B2-1665859BA500}" uniqueName="4" name="ProductID" queryTableFieldId="4" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{0E27DE63-90A7-49BC-A53A-8C102D6575E5}" uniqueName="5" name="StoreID" queryTableFieldId="5" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{F70E5803-CDE6-4E04-B0AC-E66A70250924}" uniqueName="6" name="CustomerID" queryTableFieldId="6" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{532F1CDF-B2EF-44D9-B43C-76A3BAE9BC36}" uniqueName="7" name="SalesChannel" queryTableFieldId="7" dataDxfId="9"/>
     <tableColumn id="8" xr3:uid="{DF219115-7DAF-4F57-831E-B5FC668606CD}" uniqueName="8" name="Quantity" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{CEA1D55C-0980-461E-B369-A394D9503A1E}" uniqueName="9" name="UnitPrice" queryTableFieldId="9"/>
     <tableColumn id="10" xr3:uid="{25718208-6D79-4A83-B086-6F49176BB353}" uniqueName="10" name="DiscountRate" queryTableFieldId="10"/>
     <tableColumn id="11" xr3:uid="{1D9126AB-F469-48F9-9125-E66C12F7D903}" uniqueName="11" name="UnitCostAtSale" queryTableFieldId="11"/>
-    <tableColumn id="12" xr3:uid="{5951FEE0-FB50-4863-A6CA-C10DA7CE77EF}" uniqueName="12" name="GrossSales" queryTableFieldId="12" dataDxfId="47">
+    <tableColumn id="12" xr3:uid="{5951FEE0-FB50-4863-A6CA-C10DA7CE77EF}" uniqueName="12" name="GrossSales" queryTableFieldId="12" dataDxfId="8">
       <calculatedColumnFormula>sales[[#This Row],[Quantity]]*sales[[#This Row],[UnitPrice]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{C65959FB-7C16-4C80-A22A-7E1C8CBCE117}" uniqueName="13" name="DiscountAmount" queryTableFieldId="13" dataDxfId="46">
+    <tableColumn id="13" xr3:uid="{C65959FB-7C16-4C80-A22A-7E1C8CBCE117}" uniqueName="13" name="DiscountAmount" queryTableFieldId="13" dataDxfId="7">
       <calculatedColumnFormula>sales[[#This Row],[GrossSales]]*sales[[#This Row],[DiscountRate]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{EDA06F4B-2D4B-4700-BB3A-E836A39D7CB8}" uniqueName="14" name="SalesAfterDiscount" queryTableFieldId="14" dataDxfId="45">
+    <tableColumn id="14" xr3:uid="{EDA06F4B-2D4B-4700-BB3A-E836A39D7CB8}" uniqueName="14" name="SalesAfterDiscount" queryTableFieldId="14" dataDxfId="6">
       <calculatedColumnFormula>sales[[#This Row],[GrossSales]]-sales[[#This Row],[DiscountAmount]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{8479A0C3-CBFC-4C03-A7DD-F02AD557F8DB}" uniqueName="15" name="CostOfGoodsSold" queryTableFieldId="15" dataDxfId="44">
+    <tableColumn id="15" xr3:uid="{8479A0C3-CBFC-4C03-A7DD-F02AD557F8DB}" uniqueName="15" name="CostOfGoodsSold" queryTableFieldId="15" dataDxfId="5">
       <calculatedColumnFormula>sales[[#This Row],[Quantity]]*sales[[#This Row],[UnitCostAtSale]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{F12E6300-FAA3-41A7-940B-9AA15A25AB45}" uniqueName="16" name="GrossProfit" queryTableFieldId="16" dataDxfId="43">
+    <tableColumn id="16" xr3:uid="{F12E6300-FAA3-41A7-940B-9AA15A25AB45}" uniqueName="16" name="GrossProfit" queryTableFieldId="16" dataDxfId="4">
       <calculatedColumnFormula>sales[[#This Row],[SalesAfterDiscount]]-sales[[#This Row],[CostOfGoodsSold]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{964840F7-7CD2-4093-85DA-9160DCAEBFE9}" uniqueName="17" name="GrossProfitMargin" queryTableFieldId="17" dataDxfId="42">
+    <tableColumn id="17" xr3:uid="{964840F7-7CD2-4093-85DA-9160DCAEBFE9}" uniqueName="17" name="GrossProfitMargin" queryTableFieldId="17" dataDxfId="3">
       <calculatedColumnFormula>IFERROR(sales[[#This Row],[GrossProfit]]/sales[[#This Row],[SalesAfterDiscount]],0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -52593,7 +52540,7 @@
       <c r="A7" t="s">
         <v>1177</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <f>IFERROR(B2/B5,0)</f>
         <v>30066.384704000011</v>
       </c>
@@ -52626,7 +52573,7 @@
       <c r="B2" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2">
         <v>288122.41999999993</v>
       </c>
     </row>
@@ -52634,7 +52581,7 @@
       <c r="B3" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3">
         <v>188052.87949999992</v>
       </c>
     </row>
@@ -52642,7 +52589,7 @@
       <c r="B4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4">
         <v>180583.40599999999</v>
       </c>
     </row>
@@ -52650,7 +52597,7 @@
       <c r="B5" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>175656.50200000007</v>
       </c>
     </row>
@@ -52658,7 +52605,7 @@
       <c r="B6" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6">
         <v>154034.90800000005</v>
       </c>
     </row>
@@ -52666,7 +52613,7 @@
       <c r="B7" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <v>144884.92250000004</v>
       </c>
     </row>
@@ -52674,7 +52621,7 @@
       <c r="B8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8">
         <v>140955.72699999996</v>
       </c>
     </row>
@@ -52682,7 +52629,7 @@
       <c r="B9" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9">
         <v>131299.48799999998</v>
       </c>
     </row>
@@ -52690,7 +52637,7 @@
       <c r="B10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10">
         <v>111365.31499999993</v>
       </c>
     </row>
@@ -52698,7 +52645,7 @@
       <c r="B11" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11">
         <v>102620.18999999997</v>
       </c>
     </row>
@@ -52706,7 +52653,7 @@
       <c r="B12" s="3" t="s">
         <v>1153</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12">
         <v>1617575.7579999997</v>
       </c>
     </row>
@@ -52738,7 +52685,7 @@
       <c r="B4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4">
         <v>7059129.1479999991</v>
       </c>
     </row>
@@ -52746,7 +52693,7 @@
       <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>7974063.203999998</v>
       </c>
     </row>
@@ -52754,7 +52701,7 @@
       <c r="B6" s="3" t="s">
         <v>1153</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6">
         <v>15033192.351999998</v>
       </c>
     </row>
@@ -52784,7 +52731,7 @@
       <c r="E4" s="3" t="s">
         <v>1156</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4">
         <v>10473515.613499999</v>
       </c>
     </row>
@@ -52792,7 +52739,7 @@
       <c r="E5" s="6" t="s">
         <v>1158</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5">
         <v>487328.00849999994</v>
       </c>
     </row>
@@ -52800,7 +52747,7 @@
       <c r="E6" s="6" t="s">
         <v>1159</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6">
         <v>811621.02749999985</v>
       </c>
     </row>
@@ -52808,7 +52755,7 @@
       <c r="E7" s="6" t="s">
         <v>1160</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7">
         <v>1144902.0984999998</v>
       </c>
     </row>
@@ -52816,7 +52763,7 @@
       <c r="E8" s="6" t="s">
         <v>1161</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8">
         <v>604318.01199999976</v>
       </c>
     </row>
@@ -52824,7 +52771,7 @@
       <c r="E9" s="6" t="s">
         <v>1162</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9">
         <v>1077500.9685000004</v>
       </c>
     </row>
@@ -52832,7 +52779,7 @@
       <c r="E10" s="6" t="s">
         <v>1163</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10">
         <v>941984.16449999972</v>
       </c>
     </row>
@@ -52840,7 +52787,7 @@
       <c r="E11" s="6" t="s">
         <v>1164</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11">
         <v>916527.25200000009</v>
       </c>
     </row>
@@ -52848,7 +52795,7 @@
       <c r="E12" s="6" t="s">
         <v>1165</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12">
         <v>952387.99549999984</v>
       </c>
     </row>
@@ -52856,7 +52803,7 @@
       <c r="E13" s="6" t="s">
         <v>1166</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13">
         <v>789424.58600000001</v>
       </c>
     </row>
@@ -52864,7 +52811,7 @@
       <c r="E14" s="6" t="s">
         <v>1167</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14">
         <v>1110217.6120000002</v>
       </c>
     </row>
@@ -52872,7 +52819,7 @@
       <c r="E15" s="6" t="s">
         <v>1168</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15">
         <v>913591.64949999994</v>
       </c>
     </row>
@@ -52880,7 +52827,7 @@
       <c r="E16" s="6" t="s">
         <v>1169</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16">
         <v>723712.23899999983</v>
       </c>
     </row>
@@ -52888,7 +52835,7 @@
       <c r="E17" s="3" t="s">
         <v>1157</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17">
         <v>4559676.738499999</v>
       </c>
     </row>
@@ -52896,7 +52843,7 @@
       <c r="E18" s="6" t="s">
         <v>1158</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18">
         <v>927888.87199999986</v>
       </c>
     </row>
@@ -52904,7 +52851,7 @@
       <c r="E19" s="6" t="s">
         <v>1159</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19">
         <v>587772.223</v>
       </c>
     </row>
@@ -52912,7 +52859,7 @@
       <c r="E20" s="6" t="s">
         <v>1160</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20">
         <v>894560.23499999987</v>
       </c>
     </row>
@@ -52920,7 +52867,7 @@
       <c r="E21" s="6" t="s">
         <v>1161</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21">
         <v>862036.74</v>
       </c>
     </row>
@@ -52928,7 +52875,7 @@
       <c r="E22" s="6" t="s">
         <v>1162</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22">
         <v>762797.05799999996</v>
       </c>
     </row>
@@ -52936,7 +52883,7 @@
       <c r="E23" s="6" t="s">
         <v>1163</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23">
         <v>524621.61049999995</v>
       </c>
     </row>
@@ -52944,7 +52891,7 @@
       <c r="E24" s="3" t="s">
         <v>1153</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24">
         <v>15033192.351999998</v>
       </c>
     </row>
@@ -52978,10 +52925,10 @@
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2">
         <v>2926555.0410000002</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2">
         <v>453355.04100000008</v>
       </c>
     </row>
@@ -52989,10 +52936,10 @@
       <c r="A3" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3">
         <v>2783045.4580000015</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3">
         <v>533945.45799999963</v>
       </c>
     </row>
@@ -53000,10 +52947,10 @@
       <c r="A4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>3365664.3375000004</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4">
         <v>608914.33749999991</v>
       </c>
     </row>
@@ -53011,10 +52958,10 @@
       <c r="A5" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>3002949.9580000015</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>570849.95799999975</v>
       </c>
     </row>
@@ -53022,10 +52969,10 @@
       <c r="A6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>2954977.5575000006</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6">
         <v>533627.5575</v>
       </c>
     </row>
@@ -53033,10 +52980,10 @@
       <c r="A7" s="3" t="s">
         <v>1153</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>15033192.352000006</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <v>2700692.3519999995</v>
       </c>
     </row>
